--- a/files/OEE_First_Pass_Yield.xlsx
+++ b/files/OEE_First_Pass_Yield.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L by BU" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,26 +26,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="001F2D55"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,10 +63,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,22 +81,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,17 +488,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OEE First Pass Yield</t>
@@ -467,111 +512,1678 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OEE_First_Pass_Yield.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: OEE_First_Pass_Yield.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023A</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024A</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>FY2026 Plan</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FY2027F</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>FY2028F</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>FY2029F</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>FY2030F</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Revenue (RM m)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2210</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CAGR ~9%</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>-- Banking --</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (RM m)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>412</v>
-      </c>
-      <c r="C6" t="n">
-        <v>455</v>
-      </c>
-      <c r="D6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Margin lift</t>
-        </is>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>12247.6</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>12567.5</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>12676.3</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13392.3</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>13527.2</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>13504.4</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>14149.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>-7877.8</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>-8128.3</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>-8115</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-8496.299999999999</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>-8554.6</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>-8845.299999999999</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>-9085.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4369.8</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4439.2</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4561.3</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4896</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4972.6</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>4659.2</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>5064.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>2255.6</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2176.7</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>2316.9</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>2542.7</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2454.2</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>2453.6</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>2435.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>-- Insurance --</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3914.4</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>4017.7</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4036.4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4188.8</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>4176.2</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4207.7</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4418.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>-2580.5</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>-2578.5</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>-2562.6</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-2722.3</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>-2684.6</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>-2670.1</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>-2885</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1333.8</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1439.2</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1473.8</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1466.6</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1491.6</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1537.7</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1533.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>564.5</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>593</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>533.3</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>564.5</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>596.3</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>584.6</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>607.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>-- Healthcare Services --</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>5386.5</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>5417.6</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5676.4</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>5580.9</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5810.8</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>5996.3</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>5978.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>-3462.4</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>-3566.2</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>-3782.8</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-3640.8</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>-3689.6</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>-3946.1</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>-3848.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1924.1</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1851.4</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1893.6</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1940.1</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2121.1</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>2050.2</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2130.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>874.1</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>890.5</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>924.4</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>925.8</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>892.9</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>958.2</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>-- Industrial Manufacturing --</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>6007</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>6017.6</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6231.4</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>6420.1</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>6488</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>6658.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>-3982</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>-3936.1</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>-4042.9</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-4202.5</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>-4138.9</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>-4336.3</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>-4256.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2081.5</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>2188.5</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>2147.6</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>2281.1</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>2151.6</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2402.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>774</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>796.7</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>776.3</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>763.9</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>816.5</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>786.3</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>838.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D28" s="6" t="n">
         <v>12.5</v>
       </c>
-      <c r="D7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Above peer median</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Note: placeholder demo data — not real Zava figures.</t>
-        </is>
+      <c r="E28" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>-- Property Development --</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>4652.8</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>4787.1</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>4849.4</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>4950.5</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>5053.7</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>5109.4</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>5284.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>-3086.5</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>-3113.2</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>-3071.2</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-3192.3</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>-3295.2</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>-3406.7</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>-3367</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>1566.3</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1673.9</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1778.2</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>1758.2</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1758.5</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>1702.6</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1917.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>980.5</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1091.3</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>1043.3</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>1128.8</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>1081.2</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>1154.5</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>1155.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>-- Oil &amp; Gas (downstream) --</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>4269.2</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>4477</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>4469.7</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>4585.7</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>4750.5</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>4857.9</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>4849.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>-2760.6</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>-2933.9</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>-2958</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-3035.5</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>-3110.7</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>-3094.8</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>-3235.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>1508.6</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>1511.7</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1550.2</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>1639.8</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>1763.1</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1614.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>458.2</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>418.6</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>474.4</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>511.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>-- Retail Distribution --</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>2087.9</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>2155.1</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>2249.3</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>2298.2</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>2260.5</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>2341.4</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>2432.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>-1387.5</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>-1374</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>-1456.8</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-1513.7</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>-1449.3</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>-1557.6</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>-1617</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>700.4</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>781.1</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>792.5</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>784.5</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>811.2</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>783.7</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>815.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>-- Hospitality --</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>1309.6</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1293.8</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>1326</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>1377.2</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>1387.2</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>1424.4</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>1474.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>-865.6</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>-838</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>-869.3</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-905.8</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>-897.4</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>-900.1</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>-946</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>444</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>455.9</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>456.7</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>471.4</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>524.3</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>528.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>207.4</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>208.1</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>231</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>246.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>-- Digital Infrastructure --</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>1620.7</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>1694.1</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>1759.1</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>1736.7</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>1802.9</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>1816.2</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>-1063.2</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>-1068.6</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>-1151.1</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-1117.5</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>-1152</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>-1157.9</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>-1234.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>557.6</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>625.5</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>608</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>619.2</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>650.9</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>658.2</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>667.7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>542</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>572.6</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>591.4</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>593.4</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>625.2</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>614.7</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>630.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>-- Education Services --</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>832</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>857.5</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>848.1</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>890.3</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>900.4</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>905.1</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>934.9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>-556.5</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>-550.7</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>-549.9</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-565.7</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>-589.4</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>-586.9</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>-599.2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>306.8</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>324.7</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>311</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>318.2</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>335.7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>119.6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>-- Plantation --</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>1775.5</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>1818.7</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>1849.4</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1879.2</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>1915.9</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>1931.5</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>2009.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>-1177</v>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>-1202</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>-1238.6</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-1242.4</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>-1218.4</v>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>-1219.5</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>-1333.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>598.5</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>616.7</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>610.8</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>636.8</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>697.5</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>711.9</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>330.9</v>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>352.4</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>352.4</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>379.6</v>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>18.9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
